--- a/data/trans_orig/P59-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P59-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su estado civil en 2007</t>
+          <t>Población según su estado civil en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14678</t>
+          <t>14284</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33396</t>
+          <t>34213</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>61325</t>
+          <t>62180</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>95766</t>
+          <t>95468</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>83418</t>
+          <t>82927</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>121299</t>
+          <t>123759</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,95%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1974</t>
+          <t>1983</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12409</t>
+          <t>12282</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>996</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8923</t>
+          <t>8703</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4009</t>
+          <t>4106</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15528</t>
+          <t>16169</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1904</t>
+          <t>1911</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12904</t>
+          <t>12624</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10857</t>
+          <t>10664</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>31389</t>
+          <t>29250</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>15388</t>
+          <t>15007</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>36884</t>
+          <t>37257</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>206285</t>
+          <t>205483</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>254464</t>
+          <t>254806</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>36,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>140490</t>
+          <t>139799</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>183799</t>
+          <t>183733</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>360722</t>
+          <t>357377</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>422824</t>
+          <t>429229</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>31,05%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>405204</t>
+          <t>403081</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>454529</t>
+          <t>456071</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>58,39%</t>
+          <t>58,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>65,49%</t>
+          <t>65,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>403712</t>
+          <t>401087</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>454138</t>
+          <t>450661</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>58,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,97%</t>
+          <t>65,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>818900</t>
+          <t>818700</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>889408</t>
+          <t>893134</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,24%</t>
+          <t>59,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>64,61%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23103</t>
+          <t>22510</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>47246</t>
+          <t>47133</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>96528</t>
+          <t>96758</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>137942</t>
+          <t>137711</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>127051</t>
+          <t>125384</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>176153</t>
+          <t>174171</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,02%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2134</t>
+          <t>1905</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13717</t>
+          <t>13613</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,82 +1543,82 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>10850</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>5309</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>21924</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>1,12%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>2,26%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>16739</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>9412</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>27558</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>0,87%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
           <t>1,43%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>10850</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>4850</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>20870</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>2,16%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>16739</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>9808</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>29157</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11098</t>
+          <t>10774</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>29919</t>
+          <t>30429</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10178</t>
+          <t>10374</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>27671</t>
+          <t>28522</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>24412</t>
+          <t>25172</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>51499</t>
+          <t>52087</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>277911</t>
+          <t>278445</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>337830</t>
+          <t>336567</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>188257</t>
+          <t>188044</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>239996</t>
+          <t>238193</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>479654</t>
+          <t>483341</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>559714</t>
+          <t>562020</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>29,12%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>563843</t>
+          <t>565302</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>625462</t>
+          <t>627532</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,62%</t>
+          <t>58,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>65,03%</t>
+          <t>65,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>581824</t>
+          <t>582362</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>642966</t>
+          <t>638479</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,08%</t>
+          <t>60,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>66,4%</t>
+          <t>65,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1159041</t>
+          <t>1160492</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1248823</t>
+          <t>1249298</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,05%</t>
+          <t>60,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>64,7%</t>
+          <t>64,72%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14147</t>
+          <t>13907</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>32355</t>
+          <t>32116</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>67678</t>
+          <t>71186</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>102609</t>
+          <t>104529</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>90927</t>
+          <t>89381</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>128347</t>
+          <t>130720</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,6%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1047</t>
+          <t>1048</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11974</t>
+          <t>10813</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5808</t>
+          <t>5304</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19170</t>
+          <t>19329</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9363</t>
+          <t>8289</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>26459</t>
+          <t>25832</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3141</t>
+          <t>3132</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>16775</t>
+          <t>16966</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>18719</t>
+          <t>19390</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>40555</t>
+          <t>38851</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>25018</t>
+          <t>25067</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>49276</t>
+          <t>49171</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2413,7 +2413,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>177586</t>
+          <t>179004</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>225759</t>
+          <t>224478</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>128523</t>
+          <t>130418</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>172437</t>
+          <t>170241</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>320448</t>
+          <t>320124</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>383908</t>
+          <t>386056</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,34%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>416172</t>
+          <t>416689</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>467280</t>
+          <t>464311</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>61,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>68,87%</t>
+          <t>68,43%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>382541</t>
+          <t>384592</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>434805</t>
+          <t>432808</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>56,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>63,58%</t>
+          <t>63,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>812685</t>
+          <t>808081</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>885092</t>
+          <t>885703</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>59,65%</t>
+          <t>59,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>64,97%</t>
+          <t>65,01%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>23729</t>
+          <t>23422</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>45684</t>
+          <t>45061</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>100612</t>
+          <t>100544</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>142769</t>
+          <t>143208</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>132771</t>
+          <t>129365</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>179523</t>
+          <t>179748</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,07%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>14559</t>
+          <t>14619</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>34526</t>
+          <t>35255</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>28860</t>
+          <t>28004</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>53983</t>
+          <t>53716</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>47585</t>
+          <t>47494</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>79810</t>
+          <t>79942</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,04%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>10094</t>
+          <t>10165</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>28256</t>
+          <t>28751</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>22282</t>
+          <t>21721</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>45899</t>
+          <t>44263</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>37192</t>
+          <t>36390</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>66326</t>
+          <t>64963</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>338447</t>
+          <t>340841</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>395415</t>
+          <t>400794</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>41,97%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>288011</t>
+          <t>289609</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>347423</t>
+          <t>350174</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>643609</t>
+          <t>648800</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>728852</t>
+          <t>729840</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>36,85%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>471127</t>
+          <t>468887</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>529854</t>
+          <t>529631</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>49,76%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>56,23%</t>
+          <t>56,21%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>495000</t>
+          <t>494104</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>562796</t>
+          <t>558541</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>47,66%</t>
+          <t>47,57%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>54,19%</t>
+          <t>53,78%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>983248</t>
+          <t>981015</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1068554</t>
+          <t>1068958</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>49,64%</t>
+          <t>49,53%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>53,94%</t>
+          <t>53,97%</t>
         </is>
       </c>
     </row>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>93321</t>
+          <t>94150</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>133988</t>
+          <t>136516</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>362549</t>
+          <t>367027</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>439107</t>
+          <t>440046</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>472570</t>
+          <t>469086</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>559832</t>
+          <t>554923</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,34%</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>27715</t>
+          <t>28104</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>52716</t>
+          <t>54494</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>49757</t>
+          <t>49178</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>81172</t>
+          <t>82105</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>84068</t>
+          <t>81995</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>125559</t>
+          <t>124483</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>36299</t>
+          <t>36634</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>67183</t>
+          <t>69113</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>77268</t>
+          <t>76620</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>116758</t>
+          <t>118069</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>122957</t>
+          <t>121879</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>171180</t>
+          <t>171463</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1053848</t>
+          <t>1048221</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1162057</t>
+          <t>1164703</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>796621</t>
+          <t>795026</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>897720</t>
+          <t>893177</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3850,12 +3850,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1881452</t>
+          <t>1880338</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>2025830</t>
+          <t>2024984</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,42%</t>
         </is>
       </c>
     </row>
@@ -3913,12 +3913,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1911947</t>
+          <t>1910809</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2025711</t>
+          <t>2025562</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>58,35%</t>
+          <t>58,32%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1916096</t>
+          <t>1914300</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2030039</t>
+          <t>2030841</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3963,12 +3963,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>56,65%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>60,07%</t>
+          <t>60,1%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>3857973</t>
+          <t>3863305</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>4021642</t>
+          <t>4016350</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>58,04%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>60,42%</t>
+          <t>60,34%</t>
         </is>
       </c>
     </row>
@@ -4180,7 +4180,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su estado civil en 2012</t>
+          <t>Población según su estado civil en 2012 (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4375,12 +4375,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18668</t>
+          <t>19241</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>40199</t>
+          <t>40821</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4390,12 +4390,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>75846</t>
+          <t>76264</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>111961</t>
+          <t>111986</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4425,12 +4425,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>102524</t>
+          <t>102511</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>144074</t>
+          <t>145057</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4460,12 +4460,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,36%</t>
         </is>
       </c>
     </row>
@@ -4488,12 +4488,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6826</t>
+          <t>6086</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21913</t>
+          <t>21540</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4503,12 +4503,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7857</t>
+          <t>8653</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24114</t>
+          <t>25789</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4538,12 +4538,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17957</t>
+          <t>17092</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>38516</t>
+          <t>39124</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4601,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7485</t>
+          <t>6934</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>24329</t>
+          <t>23111</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4616,12 +4616,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5813</t>
+          <t>5714</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22725</t>
+          <t>21958</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>16668</t>
+          <t>15583</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>39716</t>
+          <t>38363</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -4714,12 +4714,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>204360</t>
+          <t>205920</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>255535</t>
+          <t>256317</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4729,12 +4729,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>36,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>121991</t>
+          <t>123745</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>166360</t>
+          <t>166984</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>342099</t>
+          <t>342617</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>407642</t>
+          <t>409234</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,24%</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>394212</t>
+          <t>392646</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>447177</t>
+          <t>445477</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4842,12 +4842,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>56,04%</t>
+          <t>55,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>63,57%</t>
+          <t>63,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>405370</t>
+          <t>406595</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>456453</t>
+          <t>456054</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,23%</t>
+          <t>58,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,57%</t>
+          <t>65,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>813834</t>
+          <t>813532</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>886552</t>
+          <t>887185</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>58,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>63,34%</t>
+          <t>63,39%</t>
         </is>
       </c>
     </row>
@@ -5057,12 +5057,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25855</t>
+          <t>25048</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>49849</t>
+          <t>51291</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>90074</t>
+          <t>91063</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>131022</t>
+          <t>130519</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>126055</t>
+          <t>122228</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>172077</t>
+          <t>168774</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,25%</t>
         </is>
       </c>
     </row>
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13810</t>
+          <t>12891</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>33625</t>
+          <t>33526</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21301</t>
+          <t>20762</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>42660</t>
+          <t>44328</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>38438</t>
+          <t>39383</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>69261</t>
+          <t>70255</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11641</t>
+          <t>11229</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>30410</t>
+          <t>30372</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8520</t>
+          <t>8117</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>24963</t>
+          <t>25166</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>23545</t>
+          <t>23238</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>48083</t>
+          <t>48412</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>297221</t>
+          <t>299653</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>360682</t>
+          <t>360677</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>211423</t>
+          <t>212259</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>267754</t>
+          <t>268579</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>526110</t>
+          <t>528858</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>611171</t>
+          <t>610020</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>29,8%</t>
         </is>
       </c>
     </row>
@@ -5509,12 +5509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>574615</t>
+          <t>576788</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>643485</t>
+          <t>639001</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5524,12 +5524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>56,64%</t>
+          <t>56,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>63,43%</t>
+          <t>62,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>603588</t>
+          <t>606122</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>670766</t>
+          <t>667882</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,48%</t>
+          <t>58,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,99%</t>
+          <t>64,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1198808</t>
+          <t>1200156</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1289083</t>
+          <t>1294687</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>58,57%</t>
+          <t>58,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>62,98%</t>
+          <t>63,26%</t>
         </is>
       </c>
     </row>
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11496</t>
+          <t>11577</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>30212</t>
+          <t>32793</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>67069</t>
+          <t>66394</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>103357</t>
+          <t>103697</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>83678</t>
+          <t>83241</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>126703</t>
+          <t>123940</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,08%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14371</t>
+          <t>14838</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>37944</t>
+          <t>38891</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>25719</t>
+          <t>25827</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>51140</t>
+          <t>50900</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>45886</t>
+          <t>44836</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>78903</t>
+          <t>81172</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5096</t>
+          <t>5012</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>17669</t>
+          <t>17481</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>9877</t>
+          <t>10032</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>29618</t>
+          <t>30509</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>17700</t>
+          <t>17614</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>40451</t>
+          <t>41810</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6055,7 +6055,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>229463</t>
+          <t>230652</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>284845</t>
+          <t>285721</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>141780</t>
+          <t>146164</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>188616</t>
+          <t>190425</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>386970</t>
+          <t>389334</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>461979</t>
+          <t>464210</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>30,25%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>419687</t>
+          <t>418696</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>476387</t>
+          <t>474973</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>55,4%</t>
+          <t>55,26%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>62,88%</t>
+          <t>62,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>442717</t>
+          <t>444225</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>502288</t>
+          <t>499212</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>57,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>64,63%</t>
+          <t>64,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>875564</t>
+          <t>878906</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>956197</t>
+          <t>958283</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>57,05%</t>
+          <t>57,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>62,3%</t>
+          <t>62,44%</t>
         </is>
       </c>
     </row>
@@ -6421,12 +6421,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>28410</t>
+          <t>28477</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>54076</t>
+          <t>51830</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>119444</t>
+          <t>119423</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>163932</t>
+          <t>163868</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6471,7 +6471,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>155482</t>
+          <t>156690</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>204946</t>
+          <t>206070</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,32%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>14923</t>
+          <t>15759</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>39550</t>
+          <t>42001</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>24578</t>
+          <t>24846</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>48311</t>
+          <t>46926</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>44493</t>
+          <t>43699</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>77974</t>
+          <t>77388</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6874</t>
+          <t>6986</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>21906</t>
+          <t>21409</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>22928</t>
+          <t>23533</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>45587</t>
+          <t>45670</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>35119</t>
+          <t>34974</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>61709</t>
+          <t>62184</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>299813</t>
+          <t>300885</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>357557</t>
+          <t>359543</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>256808</t>
+          <t>255981</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>314785</t>
+          <t>316321</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>573911</t>
+          <t>574012</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>655382</t>
+          <t>655234</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>505091</t>
+          <t>505709</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>569454</t>
+          <t>568736</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>53,49%</t>
+          <t>53,56%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>60,31%</t>
+          <t>60,24%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>524378</t>
+          <t>525291</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>590272</t>
+          <t>590813</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6923,12 +6923,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>49,85%</t>
+          <t>49,94%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>56,11%</t>
+          <t>56,17%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1055413</t>
+          <t>1051014</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1143459</t>
+          <t>1142299</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>52,87%</t>
+          <t>52,65%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>57,28%</t>
+          <t>57,23%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>100717</t>
+          <t>102731</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>144927</t>
+          <t>147248</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>388414</t>
+          <t>391326</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>465018</t>
+          <t>468792</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>504940</t>
+          <t>502412</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>599533</t>
+          <t>594962</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,53%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>65238</t>
+          <t>64415</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>105719</t>
+          <t>106081</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>97214</t>
+          <t>94983</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>140812</t>
+          <t>137960</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>169354</t>
+          <t>174209</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>231182</t>
+          <t>233118</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>41594</t>
+          <t>41790</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>71969</t>
+          <t>73339</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7349,7 +7349,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>62995</t>
+          <t>60963</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>103511</t>
+          <t>98871</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>113873</t>
+          <t>111873</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>163251</t>
+          <t>161419</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1086491</t>
+          <t>1090293</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1204977</t>
+          <t>1205531</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>35,25%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>785902</t>
+          <t>783927</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>889811</t>
+          <t>892081</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1903966</t>
+          <t>1910328</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>2059966</t>
+          <t>2060689</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,53%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1953732</t>
+          <t>1957951</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2070453</t>
+          <t>2071229</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>57,13%</t>
+          <t>57,25%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>60,54%</t>
+          <t>60,57%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2039115</t>
+          <t>2036606</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2158610</t>
+          <t>2157171</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>57,32%</t>
+          <t>57,25%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>60,68%</t>
+          <t>60,64%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>4029309</t>
+          <t>4030321</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>4189042</t>
+          <t>4190681</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>57,75%</t>
+          <t>57,76%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>60,04%</t>
+          <t>60,06%</t>
         </is>
       </c>
     </row>
@@ -7822,7 +7822,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su estado civil en 2016</t>
+          <t>Población según su estado civil en 2016 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8017,12 +8017,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20253</t>
+          <t>20636</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>40089</t>
+          <t>40377</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8032,12 +8032,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>72934</t>
+          <t>73517</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>110282</t>
+          <t>110940</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8067,12 +8067,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8087,12 +8087,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>99426</t>
+          <t>99661</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>144018</t>
+          <t>144921</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8102,12 +8102,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,75%</t>
         </is>
       </c>
     </row>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8092</t>
+          <t>7307</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25238</t>
+          <t>23835</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8165,12 +8165,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16400</t>
+          <t>16058</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>37616</t>
+          <t>36743</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8180,12 +8180,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>27968</t>
+          <t>27041</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>54924</t>
+          <t>53651</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8215,12 +8215,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15058</t>
+          <t>14477</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>35279</t>
+          <t>35152</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9711</t>
+          <t>9126</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>24519</t>
+          <t>24665</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>28525</t>
+          <t>27071</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>55280</t>
+          <t>53960</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8356,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>204770</t>
+          <t>204526</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>251952</t>
+          <t>252285</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>37,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>130513</t>
+          <t>128579</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>172733</t>
+          <t>170368</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8406,47 +8406,47 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
+          <t>25,32%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>378</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>377082</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>345961</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>412607</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>27,98%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>25,67%</t>
         </is>
       </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>378</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>377082</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>347232</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>412246</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>27,98%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>25,77%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,62%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>353058</t>
+          <t>355647</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>403683</t>
+          <t>405714</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>52,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>59,82%</t>
+          <t>60,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>368429</t>
+          <t>367029</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>417500</t>
+          <t>417608</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>54,76%</t>
+          <t>54,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>62,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>732391</t>
+          <t>734559</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>804560</t>
+          <t>807873</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>54,35%</t>
+          <t>54,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>59,7%</t>
+          <t>59,95%</t>
         </is>
       </c>
     </row>
@@ -8699,12 +8699,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>34000</t>
+          <t>33961</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>57963</t>
+          <t>60244</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8714,12 +8714,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8734,12 +8734,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>96559</t>
+          <t>97398</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>140043</t>
+          <t>140169</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8749,12 +8749,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>139229</t>
+          <t>138062</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>188841</t>
+          <t>189991</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,21%</t>
         </is>
       </c>
     </row>
@@ -8812,12 +8812,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18417</t>
+          <t>18009</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>40127</t>
+          <t>39738</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8827,12 +8827,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8847,12 +8847,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26517</t>
+          <t>25402</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>51023</t>
+          <t>50139</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8862,12 +8862,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>49873</t>
+          <t>48788</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>85118</t>
+          <t>81263</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15737</t>
+          <t>16657</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>35649</t>
+          <t>37267</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>13482</t>
+          <t>12786</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>31622</t>
+          <t>30437</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>32717</t>
+          <t>32387</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>61321</t>
+          <t>59663</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>328028</t>
+          <t>326358</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>390852</t>
+          <t>389704</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>38,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>208383</t>
+          <t>210090</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>265643</t>
+          <t>263745</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9088,12 +9088,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>555722</t>
+          <t>553073</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>637339</t>
+          <t>633038</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>30,7%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>534475</t>
+          <t>537129</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>598319</t>
+          <t>599820</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>52,27%</t>
+          <t>52,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>58,52%</t>
+          <t>58,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>597540</t>
+          <t>593102</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>660234</t>
+          <t>659094</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>57,46%</t>
+          <t>57,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>63,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1151599</t>
+          <t>1152624</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1241033</t>
+          <t>1239191</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>55,84%</t>
+          <t>55,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>60,18%</t>
+          <t>60,09%</t>
         </is>
       </c>
     </row>
@@ -9381,12 +9381,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>27522</t>
+          <t>27819</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>51841</t>
+          <t>52260</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9416,12 +9416,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>65724</t>
+          <t>66530</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>105064</t>
+          <t>103401</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>103657</t>
+          <t>100202</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>147529</t>
+          <t>145206</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9466,12 +9466,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,41%</t>
         </is>
       </c>
     </row>
@@ -9494,12 +9494,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7535</t>
+          <t>7484</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23976</t>
+          <t>22914</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9514,7 +9514,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>24030</t>
+          <t>23634</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>47769</t>
+          <t>47744</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9544,47 +9544,47 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
+          <t>3,02%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>6,09%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>47451</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>34913</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>61821</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
           <t>3,07%</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>6,09%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>47451</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>34484</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>64824</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>3,07%</t>
-        </is>
-      </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9607,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>13821</t>
+          <t>13084</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>33481</t>
+          <t>32435</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>20293</t>
+          <t>20144</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>42750</t>
+          <t>41994</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9657,12 +9657,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>38816</t>
+          <t>37526</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>66055</t>
+          <t>66612</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9692,12 +9692,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -9720,12 +9720,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>230155</t>
+          <t>228961</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>281065</t>
+          <t>283164</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9735,12 +9735,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>188474</t>
+          <t>187055</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>236711</t>
+          <t>238933</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9770,12 +9770,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>432306</t>
+          <t>429464</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>504813</t>
+          <t>503746</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>32,64%</t>
         </is>
       </c>
     </row>
@@ -9833,12 +9833,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>402771</t>
+          <t>403062</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>459219</t>
+          <t>458293</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9848,12 +9848,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>53,03%</t>
+          <t>53,07%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>60,46%</t>
+          <t>60,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>391448</t>
+          <t>395769</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>452937</t>
+          <t>453922</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>49,94%</t>
+          <t>50,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>57,78%</t>
+          <t>57,91%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>819329</t>
+          <t>817411</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>893202</t>
+          <t>895444</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>53,09%</t>
+          <t>52,96%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>57,87%</t>
+          <t>58,02%</t>
         </is>
       </c>
     </row>
@@ -10063,12 +10063,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>23208</t>
+          <t>22233</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>43720</t>
+          <t>43962</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10078,12 +10078,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>121446</t>
+          <t>121132</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>172552</t>
+          <t>170962</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10113,12 +10113,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10133,12 +10133,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>152830</t>
+          <t>152433</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>207650</t>
+          <t>208283</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10148,12 +10148,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,52%</t>
         </is>
       </c>
     </row>
@@ -10176,12 +10176,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>23723</t>
+          <t>23776</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>46182</t>
+          <t>47396</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10191,12 +10191,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>50184</t>
+          <t>49406</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>83548</t>
+          <t>82226</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10226,12 +10226,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10246,12 +10246,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>80490</t>
+          <t>81798</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>121789</t>
+          <t>121169</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10261,12 +10261,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,12%</t>
         </is>
       </c>
     </row>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>18740</t>
+          <t>18822</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>40030</t>
+          <t>39689</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10304,12 +10304,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>25951</t>
+          <t>27043</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>49933</t>
+          <t>51416</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>52318</t>
+          <t>51295</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>84572</t>
+          <t>83097</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,2%</t>
         </is>
       </c>
     </row>
@@ -10402,12 +10402,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>294452</t>
+          <t>296311</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>350707</t>
+          <t>351589</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10417,12 +10417,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10437,12 +10437,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>298292</t>
+          <t>296909</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>360342</t>
+          <t>362934</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>609544</t>
+          <t>607265</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>692033</t>
+          <t>692572</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>34,97%</t>
         </is>
       </c>
     </row>
@@ -10515,12 +10515,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>490433</t>
+          <t>490415</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>549259</t>
+          <t>549067</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10535,7 +10535,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>58,64%</t>
+          <t>58,62%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10550,12 +10550,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>437099</t>
+          <t>437575</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>503033</t>
+          <t>505198</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>41,92%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>48,19%</t>
+          <t>48,4%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>944273</t>
+          <t>940826</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1033648</t>
+          <t>1032352</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>52,19%</t>
+          <t>52,13%</t>
         </is>
       </c>
     </row>
@@ -10745,12 +10745,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>123642</t>
+          <t>121431</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>169558</t>
+          <t>164549</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10760,12 +10760,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10780,12 +10780,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>392327</t>
+          <t>394524</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>487646</t>
+          <t>479542</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>531838</t>
+          <t>534374</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>633940</t>
+          <t>629791</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,08%</t>
         </is>
       </c>
     </row>
@@ -10858,12 +10858,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>71408</t>
+          <t>69745</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>109719</t>
+          <t>109680</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10873,7 +10873,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>136370</t>
+          <t>135882</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>187837</t>
+          <t>186631</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>217293</t>
+          <t>216739</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>282041</t>
+          <t>282762</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10948,7 +10948,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -10971,12 +10971,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>77968</t>
+          <t>77673</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>118063</t>
+          <t>118015</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10986,7 +10986,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>84190</t>
+          <t>84704</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>122742</t>
+          <t>125152</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>175957</t>
+          <t>173416</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>234054</t>
+          <t>233124</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -11084,12 +11084,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1109617</t>
+          <t>1103490</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1224941</t>
+          <t>1223569</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11099,12 +11099,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11119,12 +11119,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>875474</t>
+          <t>869987</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>981993</t>
+          <t>971267</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11134,12 +11134,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11154,12 +11154,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2012113</t>
+          <t>2011453</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>2165104</t>
+          <t>2160904</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>31,16%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1836514</t>
+          <t>1838012</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1957058</t>
+          <t>1960274</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>54,12%</t>
+          <t>54,16%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>57,67%</t>
+          <t>57,77%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1848975</t>
+          <t>1853401</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1975845</t>
+          <t>1972398</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>52,23%</t>
+          <t>52,35%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>55,81%</t>
+          <t>55,71%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>3731652</t>
+          <t>3740450</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3893885</t>
+          <t>3901921</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>53,94%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>56,16%</t>
+          <t>56,27%</t>
         </is>
       </c>
     </row>
@@ -11464,7 +11464,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su estado civil en 2023</t>
+          <t>Población según su estado civil en 2023 (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11659,12 +11659,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27573</t>
+          <t>28271</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47872</t>
+          <t>48139</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11674,12 +11674,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11694,12 +11694,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>99694</t>
+          <t>100855</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>126648</t>
+          <t>127679</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11709,12 +11709,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11729,12 +11729,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>133497</t>
+          <t>131522</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>164994</t>
+          <t>164072</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11744,12 +11744,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,53%</t>
         </is>
       </c>
     </row>
@@ -11772,12 +11772,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21666</t>
+          <t>20780</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>43273</t>
+          <t>42649</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11787,12 +11787,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11807,12 +11807,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18218</t>
+          <t>18829</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33008</t>
+          <t>32560</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11822,12 +11822,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11842,12 +11842,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>42892</t>
+          <t>43211</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>69573</t>
+          <t>67467</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11857,12 +11857,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -11885,12 +11885,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12033</t>
+          <t>11683</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29979</t>
+          <t>28407</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11900,12 +11900,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11920,12 +11920,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11977</t>
+          <t>12417</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>25059</t>
+          <t>25537</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11935,12 +11935,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11955,12 +11955,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>28264</t>
+          <t>27684</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>49896</t>
+          <t>48112</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11970,12 +11970,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,67%</t>
         </is>
       </c>
     </row>
@@ -11998,12 +11998,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>230356</t>
+          <t>229663</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>287099</t>
+          <t>287230</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>45,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -12033,12 +12033,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>144971</t>
+          <t>145030</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>187648</t>
+          <t>185645</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -12048,12 +12048,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -12068,12 +12068,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>387734</t>
+          <t>390702</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>463363</t>
+          <t>464407</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -12083,12 +12083,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>35,46%</t>
         </is>
       </c>
     </row>
@@ -12111,12 +12111,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>264622</t>
+          <t>267480</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>318847</t>
+          <t>318060</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -12126,12 +12126,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>42,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>50,18%</t>
+          <t>50,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12146,12 +12146,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>331842</t>
+          <t>333190</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>372854</t>
+          <t>377214</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -12161,12 +12161,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>49,23%</t>
+          <t>49,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>55,31%</t>
+          <t>55,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12181,12 +12181,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>608264</t>
+          <t>607472</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>680974</t>
+          <t>679504</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -12196,12 +12196,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,45%</t>
+          <t>46,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>51,89%</t>
         </is>
       </c>
     </row>
@@ -12341,12 +12341,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22612</t>
+          <t>23139</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>70524</t>
+          <t>71692</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -12356,12 +12356,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12376,12 +12376,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>101444</t>
+          <t>102161</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>130185</t>
+          <t>130706</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -12391,12 +12391,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12411,12 +12411,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>113189</t>
+          <t>105332</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>191681</t>
+          <t>192751</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -12426,12 +12426,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,98%</t>
         </is>
       </c>
     </row>
@@ -12454,12 +12454,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11707</t>
+          <t>10936</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>35126</t>
+          <t>35885</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -12469,12 +12469,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12489,12 +12489,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>44292</t>
+          <t>44398</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>67630</t>
+          <t>68363</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -12504,12 +12504,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12524,12 +12524,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>49564</t>
+          <t>52204</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>96669</t>
+          <t>96639</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -12539,7 +12539,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -12567,12 +12567,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9605</t>
+          <t>9292</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>31334</t>
+          <t>30854</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -12582,12 +12582,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12602,12 +12602,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>23227</t>
+          <t>23265</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>39578</t>
+          <t>40737</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -12617,12 +12617,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12637,12 +12637,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>34412</t>
+          <t>33469</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>63899</t>
+          <t>63759</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -12680,12 +12680,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>189352</t>
+          <t>180608</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>495672</t>
+          <t>491863</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12695,12 +12695,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12715,12 +12715,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>207234</t>
+          <t>208499</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>261242</t>
+          <t>263481</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12730,12 +12730,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12750,12 +12750,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>404639</t>
+          <t>401869</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>704491</t>
+          <t>706791</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12765,12 +12765,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>32,93%</t>
         </is>
       </c>
     </row>
@@ -12793,12 +12793,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>588566</t>
+          <t>587881</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>951522</t>
+          <t>967442</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12808,12 +12808,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>49,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>495367</t>
+          <t>493189</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>548739</t>
+          <t>545476</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12843,12 +12843,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>51,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>57,44%</t>
+          <t>57,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12863,12 +12863,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1113994</t>
+          <t>1119454</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1532000</t>
+          <t>1557874</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12878,12 +12878,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>51,9%</t>
+          <t>52,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,37%</t>
+          <t>72,58%</t>
         </is>
       </c>
     </row>
@@ -13023,12 +13023,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>21115</t>
+          <t>20998</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>40589</t>
+          <t>40919</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -13038,12 +13038,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13058,12 +13058,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>43647</t>
+          <t>39648</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>116592</t>
+          <t>116567</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -13073,7 +13073,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -13093,12 +13093,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>74880</t>
+          <t>73418</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>140607</t>
+          <t>140982</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -13108,12 +13108,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,64%</t>
         </is>
       </c>
     </row>
@@ -13136,12 +13136,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21768</t>
+          <t>23570</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>45180</t>
+          <t>45382</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -13151,12 +13151,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13171,12 +13171,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20626</t>
+          <t>18249</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>62250</t>
+          <t>61963</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -13186,12 +13186,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13206,12 +13206,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>50173</t>
+          <t>48796</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>96238</t>
+          <t>96104</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -13221,7 +13221,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -13249,12 +13249,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18003</t>
+          <t>18805</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>40316</t>
+          <t>40967</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13264,12 +13264,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13284,12 +13284,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>13539</t>
+          <t>12665</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>40640</t>
+          <t>41018</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -13299,12 +13299,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13319,12 +13319,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>36929</t>
+          <t>36897</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>73067</t>
+          <t>73427</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -13339,7 +13339,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -13362,12 +13362,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>224064</t>
+          <t>224246</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>290710</t>
+          <t>290690</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -13377,12 +13377,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>41,4%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13397,12 +13397,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>94937</t>
+          <t>93132</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>249526</t>
+          <t>249033</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -13412,12 +13412,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13432,12 +13432,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>299192</t>
+          <t>273926</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>524225</t>
+          <t>517181</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -13447,12 +13447,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>31,68%</t>
         </is>
       </c>
     </row>
@@ -13475,12 +13475,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>323392</t>
+          <t>322095</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>386354</t>
+          <t>387926</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -13490,12 +13490,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>46,06%</t>
+          <t>45,88%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>55,03%</t>
+          <t>55,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13510,12 +13510,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>475071</t>
+          <t>476402</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>758855</t>
+          <t>766657</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -13525,12 +13525,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>51,06%</t>
+          <t>51,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,56%</t>
+          <t>82,4%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13545,12 +13545,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>824351</t>
+          <t>833181</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1170316</t>
+          <t>1203177</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -13560,12 +13560,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>50,49%</t>
+          <t>51,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>71,69%</t>
+          <t>73,7%</t>
         </is>
       </c>
     </row>
@@ -13705,12 +13705,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>34788</t>
+          <t>36366</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>57088</t>
+          <t>57613</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13720,12 +13720,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13740,12 +13740,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>127544</t>
+          <t>125114</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>178731</t>
+          <t>177915</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13755,12 +13755,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13775,12 +13775,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>175300</t>
+          <t>175600</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>227544</t>
+          <t>224470</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13790,12 +13790,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,13%</t>
         </is>
       </c>
     </row>
@@ -13818,12 +13818,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>33339</t>
+          <t>32145</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>57702</t>
+          <t>58051</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13833,12 +13833,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13853,12 +13853,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>53121</t>
+          <t>52029</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>85958</t>
+          <t>89216</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13868,12 +13868,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13888,12 +13888,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>93501</t>
+          <t>92521</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>133564</t>
+          <t>132798</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13903,12 +13903,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,58%</t>
         </is>
       </c>
     </row>
@@ -13931,12 +13931,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>15513</t>
+          <t>14929</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>32841</t>
+          <t>32610</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13946,12 +13946,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13966,12 +13966,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>31454</t>
+          <t>32443</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>56506</t>
+          <t>56351</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13981,12 +13981,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14001,12 +14001,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>52505</t>
+          <t>51870</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>83745</t>
+          <t>81220</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -14016,12 +14016,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -14044,12 +14044,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>324086</t>
+          <t>324736</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>396925</t>
+          <t>391957</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>42,4%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14079,12 +14079,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>329178</t>
+          <t>330454</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>521737</t>
+          <t>519676</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -14094,12 +14094,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>47,76%</t>
+          <t>47,57%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14114,12 +14114,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>680794</t>
+          <t>680694</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>904894</t>
+          <t>894791</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -14134,7 +14134,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>44,36%</t>
         </is>
       </c>
     </row>
@@ -14157,12 +14157,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>417629</t>
+          <t>423729</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>483583</t>
+          <t>486584</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -14172,12 +14172,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>45,83%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>52,63%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14192,12 +14192,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>344209</t>
+          <t>355290</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>476279</t>
+          <t>477486</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -14207,12 +14207,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>43,71%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14227,12 +14227,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>790301</t>
+          <t>786276</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>948517</t>
+          <t>947387</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14242,12 +14242,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>38,98%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>46,97%</t>
         </is>
       </c>
     </row>
@@ -14387,12 +14387,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>122405</t>
+          <t>122825</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>190293</t>
+          <t>188261</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -14402,12 +14402,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -14422,12 +14422,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>393196</t>
+          <t>372696</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>513983</t>
+          <t>513260</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -14457,12 +14457,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>549124</t>
+          <t>548078</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>683328</t>
+          <t>681060</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -14472,12 +14472,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,58%</t>
         </is>
       </c>
     </row>
@@ -14500,12 +14500,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>96911</t>
+          <t>99241</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>153457</t>
+          <t>154782</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -14515,12 +14515,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14535,12 +14535,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>156174</t>
+          <t>155161</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>220607</t>
+          <t>220683</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -14550,7 +14550,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -14570,12 +14570,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>272328</t>
+          <t>274572</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>360549</t>
+          <t>358058</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -14585,12 +14585,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -14613,12 +14613,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>69157</t>
+          <t>68665</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>112411</t>
+          <t>112901</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -14628,12 +14628,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14648,12 +14648,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>96678</t>
+          <t>97407</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>141029</t>
+          <t>139536</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14663,12 +14663,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14683,12 +14683,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>179268</t>
+          <t>175811</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>240782</t>
+          <t>240374</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14698,12 +14698,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -14726,12 +14726,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>976889</t>
+          <t>972577</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1372141</t>
+          <t>1369591</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14741,12 +14741,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>39,74%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14761,12 +14761,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>821323</t>
+          <t>814305</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1126463</t>
+          <t>1101710</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14776,12 +14776,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14796,12 +14796,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1938918</t>
+          <t>1935487</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>2419597</t>
+          <t>2405135</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -14811,12 +14811,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>33,85%</t>
         </is>
       </c>
     </row>
@@ -14839,12 +14839,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1676621</t>
+          <t>1681939</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2172806</t>
+          <t>2176785</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -14854,12 +14854,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>48,71%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>62,92%</t>
+          <t>63,04%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14874,12 +14874,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1748271</t>
+          <t>1767049</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2193736</t>
+          <t>2235060</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -14889,12 +14889,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>47,87%</t>
+          <t>48,38%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>60,07%</t>
+          <t>61,2%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14909,12 +14909,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>3487280</t>
+          <t>3508135</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>4178566</t>
+          <t>4166513</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14924,12 +14924,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>49,08%</t>
+          <t>49,37%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>58,81%</t>
+          <t>58,64%</t>
         </is>
       </c>
     </row>
